--- a/server/excel/release/recharge-item.xlsx
+++ b/server/excel/release/recharge-item.xlsx
@@ -5873,7 +5873,7 @@
         <v>14</v>
       </c>
       <c r="C4" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D4"/>
       <c r="E4"/>
@@ -5900,7 +5900,7 @@
         <v>16</v>
       </c>
       <c r="C5" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D5"/>
       <c r="E5"/>
@@ -5927,7 +5927,7 @@
         <v>17</v>
       </c>
       <c r="C6" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D6"/>
       <c r="E6"/>
@@ -6008,7 +6008,7 @@
         <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D9"/>
       <c r="E9"/>
@@ -6035,7 +6035,7 @@
         <v>21</v>
       </c>
       <c r="C10" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D10"/>
       <c r="E10"/>
@@ -6062,7 +6062,7 @@
         <v>22</v>
       </c>
       <c r="C11" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D11"/>
       <c r="E11"/>
@@ -6953,7 +6953,7 @@
         <v>59</v>
       </c>
       <c r="C44" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D44"/>
       <c r="E44"/>
@@ -6980,7 +6980,7 @@
         <v>60</v>
       </c>
       <c r="C45" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D45"/>
       <c r="E45"/>
@@ -7007,7 +7007,7 @@
         <v>61</v>
       </c>
       <c r="C46" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D46"/>
       <c r="E46"/>
@@ -7088,7 +7088,7 @@
         <v>64</v>
       </c>
       <c r="C49" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D49"/>
       <c r="E49"/>
@@ -7115,7 +7115,7 @@
         <v>65</v>
       </c>
       <c r="C50" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D50"/>
       <c r="E50"/>
@@ -7142,7 +7142,7 @@
         <v>66</v>
       </c>
       <c r="C51" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D51"/>
       <c r="E51"/>
@@ -11762,7 +11762,7 @@
         <v>141</v>
       </c>
       <c r="C222" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D222"/>
       <c r="E222"/>
@@ -11789,7 +11789,7 @@
         <v>141</v>
       </c>
       <c r="C223" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D223"/>
       <c r="E223"/>
@@ -11816,7 +11816,7 @@
         <v>142</v>
       </c>
       <c r="C224" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D224"/>
       <c r="E224"/>
@@ -11843,7 +11843,7 @@
         <v>142</v>
       </c>
       <c r="C225" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D225"/>
       <c r="E225"/>
@@ -11870,7 +11870,7 @@
         <v>142</v>
       </c>
       <c r="C226" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D226"/>
       <c r="E226"/>
@@ -11897,7 +11897,7 @@
         <v>143</v>
       </c>
       <c r="C227" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D227"/>
       <c r="E227"/>
@@ -11924,7 +11924,7 @@
         <v>144</v>
       </c>
       <c r="C228" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D228"/>
       <c r="E228"/>
@@ -12167,7 +12167,7 @@
         <v>153</v>
       </c>
       <c r="C237" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D237"/>
       <c r="E237"/>
@@ -12248,7 +12248,7 @@
         <v>156</v>
       </c>
       <c r="C240" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D240"/>
       <c r="E240"/>
@@ -12275,7 +12275,7 @@
         <v>157</v>
       </c>
       <c r="C241" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D241"/>
       <c r="E241"/>
@@ -12302,7 +12302,7 @@
         <v>158</v>
       </c>
       <c r="C242" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D242"/>
       <c r="E242"/>
@@ -12329,7 +12329,7 @@
         <v>159</v>
       </c>
       <c r="C243" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D243"/>
       <c r="E243"/>
@@ -12356,7 +12356,7 @@
         <v>160</v>
       </c>
       <c r="C244" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D244"/>
       <c r="E244"/>
@@ -12383,7 +12383,7 @@
         <v>161</v>
       </c>
       <c r="C245" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D245"/>
       <c r="E245"/>
@@ -12410,7 +12410,7 @@
         <v>162</v>
       </c>
       <c r="C246" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D246"/>
       <c r="E246"/>
@@ -12437,7 +12437,7 @@
         <v>163</v>
       </c>
       <c r="C247" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D247"/>
       <c r="E247"/>
@@ -12464,7 +12464,7 @@
         <v>164</v>
       </c>
       <c r="C248" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D248"/>
       <c r="E248"/>
@@ -12491,7 +12491,7 @@
         <v>165</v>
       </c>
       <c r="C249" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D249"/>
       <c r="E249"/>
@@ -12518,7 +12518,7 @@
         <v>166</v>
       </c>
       <c r="C250" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D250"/>
       <c r="E250"/>
@@ -12545,7 +12545,7 @@
         <v>167</v>
       </c>
       <c r="C251" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D251"/>
       <c r="E251"/>
@@ -12572,7 +12572,7 @@
         <v>168</v>
       </c>
       <c r="C252" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D252"/>
       <c r="E252"/>
@@ -12599,7 +12599,7 @@
         <v>169</v>
       </c>
       <c r="C253" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D253"/>
       <c r="E253"/>
@@ -12626,7 +12626,7 @@
         <v>170</v>
       </c>
       <c r="C254" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D254"/>
       <c r="E254"/>
@@ -12653,7 +12653,7 @@
         <v>171</v>
       </c>
       <c r="C255" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D255"/>
       <c r="E255"/>
@@ -12680,7 +12680,7 @@
         <v>172</v>
       </c>
       <c r="C256" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D256"/>
       <c r="E256"/>
@@ -12707,7 +12707,7 @@
         <v>173</v>
       </c>
       <c r="C257" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D257"/>
       <c r="E257"/>
@@ -12734,7 +12734,7 @@
         <v>174</v>
       </c>
       <c r="C258" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D258"/>
       <c r="E258"/>
@@ -12761,7 +12761,7 @@
         <v>175</v>
       </c>
       <c r="C259" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D259"/>
       <c r="E259"/>
@@ -12788,7 +12788,7 @@
         <v>176</v>
       </c>
       <c r="C260" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D260"/>
       <c r="E260"/>
@@ -12815,7 +12815,7 @@
         <v>177</v>
       </c>
       <c r="C261" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D261"/>
       <c r="E261"/>
@@ -12842,7 +12842,7 @@
         <v>178</v>
       </c>
       <c r="C262" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D262"/>
       <c r="E262"/>
@@ -15515,7 +15515,7 @@
         <v>271</v>
       </c>
       <c r="C361" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D361"/>
       <c r="E361"/>
@@ -15623,7 +15623,7 @@
         <v>275</v>
       </c>
       <c r="C365" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D365"/>
       <c r="E365"/>
@@ -16433,7 +16433,7 @@
         <v>305</v>
       </c>
       <c r="C395" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D395"/>
       <c r="E395"/>
@@ -16460,7 +16460,7 @@
         <v>306</v>
       </c>
       <c r="C396" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D396"/>
       <c r="E396"/>
@@ -16568,7 +16568,7 @@
         <v>310</v>
       </c>
       <c r="C400" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D400"/>
       <c r="E400"/>
@@ -26531,7 +26531,7 @@
         <v>554</v>
       </c>
       <c r="C769" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D769"/>
       <c r="E769"/>
@@ -27044,7 +27044,7 @@
         <v>557</v>
       </c>
       <c r="C788" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D788"/>
       <c r="E788"/>
@@ -27098,7 +27098,7 @@
         <v>559</v>
       </c>
       <c r="C790" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D790"/>
       <c r="E790"/>
@@ -27179,7 +27179,7 @@
         <v>562</v>
       </c>
       <c r="C793" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D793"/>
       <c r="E793"/>
@@ -27206,7 +27206,7 @@
         <v>563</v>
       </c>
       <c r="C794" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D794"/>
       <c r="E794"/>
@@ -27233,7 +27233,7 @@
         <v>564</v>
       </c>
       <c r="C795" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D795"/>
       <c r="E795"/>
@@ -27260,7 +27260,7 @@
         <v>565</v>
       </c>
       <c r="C796" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D796"/>
       <c r="E796"/>
@@ -27287,7 +27287,7 @@
         <v>566</v>
       </c>
       <c r="C797" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D797"/>
       <c r="E797"/>
@@ -27314,7 +27314,7 @@
         <v>568</v>
       </c>
       <c r="C798" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D798"/>
       <c r="E798"/>
@@ -27341,7 +27341,7 @@
         <v>570</v>
       </c>
       <c r="C799" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D799"/>
       <c r="E799"/>
@@ -27368,7 +27368,7 @@
         <v>572</v>
       </c>
       <c r="C800" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D800"/>
       <c r="E800"/>
@@ -27395,7 +27395,7 @@
         <v>574</v>
       </c>
       <c r="C801" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D801"/>
       <c r="E801"/>
@@ -27422,7 +27422,7 @@
         <v>576</v>
       </c>
       <c r="C802" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D802"/>
       <c r="E802"/>
@@ -27449,7 +27449,7 @@
         <v>578</v>
       </c>
       <c r="C803" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D803"/>
       <c r="E803"/>
@@ -27476,7 +27476,7 @@
         <v>580</v>
       </c>
       <c r="C804" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D804"/>
       <c r="E804"/>
@@ -27503,7 +27503,7 @@
         <v>582</v>
       </c>
       <c r="C805" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D805"/>
       <c r="E805"/>
@@ -27530,7 +27530,7 @@
         <v>584</v>
       </c>
       <c r="C806" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D806"/>
       <c r="E806"/>
@@ -27557,7 +27557,7 @@
         <v>586</v>
       </c>
       <c r="C807" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D807"/>
       <c r="E807"/>
@@ -27584,7 +27584,7 @@
         <v>588</v>
       </c>
       <c r="C808" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D808"/>
       <c r="E808"/>
@@ -27611,7 +27611,7 @@
         <v>590</v>
       </c>
       <c r="C809" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D809"/>
       <c r="E809"/>
@@ -27638,7 +27638,7 @@
         <v>592</v>
       </c>
       <c r="C810" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D810"/>
       <c r="E810"/>
@@ -27665,7 +27665,7 @@
         <v>594</v>
       </c>
       <c r="C811" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D811"/>
       <c r="E811"/>
@@ -27692,7 +27692,7 @@
         <v>596</v>
       </c>
       <c r="C812" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D812"/>
       <c r="E812"/>
@@ -27719,7 +27719,7 @@
         <v>598</v>
       </c>
       <c r="C813" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D813"/>
       <c r="E813"/>
@@ -27746,7 +27746,7 @@
         <v>600</v>
       </c>
       <c r="C814" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D814"/>
       <c r="E814"/>
@@ -27773,7 +27773,7 @@
         <v>602</v>
       </c>
       <c r="C815" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D815"/>
       <c r="E815"/>
@@ -27800,7 +27800,7 @@
         <v>604</v>
       </c>
       <c r="C816" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D816"/>
       <c r="E816"/>
@@ -27827,7 +27827,7 @@
         <v>606</v>
       </c>
       <c r="C817" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D817"/>
       <c r="E817"/>
@@ -27854,7 +27854,7 @@
         <v>608</v>
       </c>
       <c r="C818" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D818"/>
       <c r="E818"/>
@@ -27881,7 +27881,7 @@
         <v>610</v>
       </c>
       <c r="C819" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D819"/>
       <c r="E819"/>
@@ -27908,7 +27908,7 @@
         <v>612</v>
       </c>
       <c r="C820" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D820"/>
       <c r="E820"/>
@@ -27935,7 +27935,7 @@
         <v>614</v>
       </c>
       <c r="C821" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D821"/>
       <c r="E821"/>
@@ -27962,7 +27962,7 @@
         <v>616</v>
       </c>
       <c r="C822" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D822"/>
       <c r="E822"/>
@@ -27989,7 +27989,7 @@
         <v>618</v>
       </c>
       <c r="C823" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D823"/>
       <c r="E823"/>
@@ -28016,7 +28016,7 @@
         <v>620</v>
       </c>
       <c r="C824" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D824"/>
       <c r="E824"/>
@@ -28043,7 +28043,7 @@
         <v>622</v>
       </c>
       <c r="C825" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D825"/>
       <c r="E825"/>
@@ -28070,7 +28070,7 @@
         <v>624</v>
       </c>
       <c r="C826" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D826"/>
       <c r="E826"/>
@@ -28097,7 +28097,7 @@
         <v>626</v>
       </c>
       <c r="C827" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D827"/>
       <c r="E827"/>
@@ -28124,7 +28124,7 @@
         <v>628</v>
       </c>
       <c r="C828" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D828"/>
       <c r="E828"/>
@@ -28151,7 +28151,7 @@
         <v>630</v>
       </c>
       <c r="C829" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D829"/>
       <c r="E829"/>
@@ -28178,7 +28178,7 @@
         <v>632</v>
       </c>
       <c r="C830" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D830"/>
       <c r="E830"/>
@@ -28205,7 +28205,7 @@
         <v>634</v>
       </c>
       <c r="C831" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D831"/>
       <c r="E831"/>
@@ -28232,7 +28232,7 @@
         <v>637</v>
       </c>
       <c r="C832" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D832"/>
       <c r="E832"/>
@@ -28259,7 +28259,7 @@
         <v>640</v>
       </c>
       <c r="C833" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D833"/>
       <c r="E833"/>
@@ -28286,7 +28286,7 @@
         <v>643</v>
       </c>
       <c r="C834" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D834"/>
       <c r="E834"/>
@@ -28313,7 +28313,7 @@
         <v>646</v>
       </c>
       <c r="C835" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D835"/>
       <c r="E835"/>
@@ -28340,7 +28340,7 @@
         <v>648</v>
       </c>
       <c r="C836" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D836"/>
       <c r="E836"/>
@@ -28367,7 +28367,7 @@
         <v>649</v>
       </c>
       <c r="C837" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D837"/>
       <c r="E837"/>
@@ -28394,7 +28394,7 @@
         <v>651</v>
       </c>
       <c r="C838" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D838"/>
       <c r="E838"/>
@@ -28421,7 +28421,7 @@
         <v>654</v>
       </c>
       <c r="C839" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D839"/>
       <c r="E839"/>
@@ -28448,7 +28448,7 @@
         <v>656</v>
       </c>
       <c r="C840" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D840"/>
       <c r="E840"/>
@@ -28475,7 +28475,7 @@
         <v>657</v>
       </c>
       <c r="C841" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D841"/>
       <c r="E841"/>
@@ -28502,7 +28502,7 @@
         <v>658</v>
       </c>
       <c r="C842" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D842"/>
       <c r="E842"/>
@@ -28529,7 +28529,7 @@
         <v>659</v>
       </c>
       <c r="C843" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D843"/>
       <c r="E843"/>
@@ -28556,7 +28556,7 @@
         <v>661</v>
       </c>
       <c r="C844" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D844"/>
       <c r="E844"/>
@@ -28583,7 +28583,7 @@
         <v>662</v>
       </c>
       <c r="C845" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D845"/>
       <c r="E845"/>
@@ -28610,7 +28610,7 @@
         <v>663</v>
       </c>
       <c r="C846" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D846"/>
       <c r="E846"/>
@@ -28637,7 +28637,7 @@
         <v>568</v>
       </c>
       <c r="C847" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D847"/>
       <c r="E847"/>
@@ -28664,7 +28664,7 @@
         <v>570</v>
       </c>
       <c r="C848" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D848"/>
       <c r="E848"/>
@@ -28691,7 +28691,7 @@
         <v>572</v>
       </c>
       <c r="C849" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D849"/>
       <c r="E849"/>
@@ -28718,7 +28718,7 @@
         <v>574</v>
       </c>
       <c r="C850" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D850"/>
       <c r="E850"/>
@@ -28745,7 +28745,7 @@
         <v>576</v>
       </c>
       <c r="C851" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D851"/>
       <c r="E851"/>
@@ -28772,7 +28772,7 @@
         <v>578</v>
       </c>
       <c r="C852" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D852"/>
       <c r="E852"/>
@@ -28799,7 +28799,7 @@
         <v>580</v>
       </c>
       <c r="C853" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D853"/>
       <c r="E853"/>
@@ -28826,7 +28826,7 @@
         <v>582</v>
       </c>
       <c r="C854" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D854"/>
       <c r="E854"/>
@@ -28853,7 +28853,7 @@
         <v>584</v>
       </c>
       <c r="C855" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D855"/>
       <c r="E855"/>
@@ -28880,7 +28880,7 @@
         <v>586</v>
       </c>
       <c r="C856" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D856"/>
       <c r="E856"/>
@@ -28907,7 +28907,7 @@
         <v>588</v>
       </c>
       <c r="C857" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D857"/>
       <c r="E857"/>
@@ -28934,7 +28934,7 @@
         <v>590</v>
       </c>
       <c r="C858" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D858"/>
       <c r="E858"/>
@@ -28961,7 +28961,7 @@
         <v>592</v>
       </c>
       <c r="C859" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D859"/>
       <c r="E859"/>
@@ -28988,7 +28988,7 @@
         <v>594</v>
       </c>
       <c r="C860" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D860"/>
       <c r="E860"/>
@@ -29015,7 +29015,7 @@
         <v>596</v>
       </c>
       <c r="C861" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D861"/>
       <c r="E861"/>
@@ -29042,7 +29042,7 @@
         <v>598</v>
       </c>
       <c r="C862" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D862"/>
       <c r="E862"/>
@@ -29069,7 +29069,7 @@
         <v>600</v>
       </c>
       <c r="C863" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D863"/>
       <c r="E863"/>
@@ -29096,7 +29096,7 @@
         <v>602</v>
       </c>
       <c r="C864" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D864"/>
       <c r="E864"/>
@@ -29123,7 +29123,7 @@
         <v>604</v>
       </c>
       <c r="C865" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D865"/>
       <c r="E865"/>
@@ -29150,7 +29150,7 @@
         <v>606</v>
       </c>
       <c r="C866" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D866"/>
       <c r="E866"/>
@@ -29177,7 +29177,7 @@
         <v>608</v>
       </c>
       <c r="C867" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D867"/>
       <c r="E867"/>
@@ -29204,7 +29204,7 @@
         <v>610</v>
       </c>
       <c r="C868" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D868"/>
       <c r="E868"/>
@@ -29231,7 +29231,7 @@
         <v>612</v>
       </c>
       <c r="C869" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D869"/>
       <c r="E869"/>
@@ -29258,7 +29258,7 @@
         <v>614</v>
       </c>
       <c r="C870" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D870"/>
       <c r="E870"/>
@@ -29285,7 +29285,7 @@
         <v>616</v>
       </c>
       <c r="C871" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D871"/>
       <c r="E871"/>
@@ -29312,7 +29312,7 @@
         <v>618</v>
       </c>
       <c r="C872" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D872"/>
       <c r="E872"/>
@@ -29339,7 +29339,7 @@
         <v>620</v>
       </c>
       <c r="C873" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D873"/>
       <c r="E873"/>
@@ -29366,7 +29366,7 @@
         <v>622</v>
       </c>
       <c r="C874" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D874"/>
       <c r="E874"/>
@@ -29393,7 +29393,7 @@
         <v>624</v>
       </c>
       <c r="C875" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D875"/>
       <c r="E875"/>
@@ -29420,7 +29420,7 @@
         <v>626</v>
       </c>
       <c r="C876" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D876"/>
       <c r="E876"/>
@@ -29447,7 +29447,7 @@
         <v>628</v>
       </c>
       <c r="C877" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D877"/>
       <c r="E877"/>
@@ -29474,7 +29474,7 @@
         <v>630</v>
       </c>
       <c r="C878" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D878"/>
       <c r="E878"/>
@@ -29501,7 +29501,7 @@
         <v>632</v>
       </c>
       <c r="C879" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D879"/>
       <c r="E879"/>
@@ -29528,7 +29528,7 @@
         <v>634</v>
       </c>
       <c r="C880" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D880"/>
       <c r="E880"/>
@@ -29555,7 +29555,7 @@
         <v>637</v>
       </c>
       <c r="C881" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D881"/>
       <c r="E881"/>
@@ -29582,7 +29582,7 @@
         <v>640</v>
       </c>
       <c r="C882" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D882"/>
       <c r="E882"/>
@@ -29609,7 +29609,7 @@
         <v>643</v>
       </c>
       <c r="C883" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D883"/>
       <c r="E883"/>
@@ -29636,7 +29636,7 @@
         <v>646</v>
       </c>
       <c r="C884" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D884"/>
       <c r="E884"/>
@@ -29663,7 +29663,7 @@
         <v>648</v>
       </c>
       <c r="C885" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D885"/>
       <c r="E885"/>
@@ -29690,7 +29690,7 @@
         <v>649</v>
       </c>
       <c r="C886" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D886"/>
       <c r="E886"/>
@@ -29717,7 +29717,7 @@
         <v>651</v>
       </c>
       <c r="C887" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D887"/>
       <c r="E887"/>
@@ -29744,7 +29744,7 @@
         <v>654</v>
       </c>
       <c r="C888" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D888"/>
       <c r="E888"/>
@@ -29771,7 +29771,7 @@
         <v>656</v>
       </c>
       <c r="C889" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D889"/>
       <c r="E889"/>
@@ -29798,7 +29798,7 @@
         <v>657</v>
       </c>
       <c r="C890" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D890"/>
       <c r="E890"/>
@@ -29825,7 +29825,7 @@
         <v>658</v>
       </c>
       <c r="C891" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D891"/>
       <c r="E891"/>
@@ -29852,7 +29852,7 @@
         <v>659</v>
       </c>
       <c r="C892" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D892"/>
       <c r="E892"/>
@@ -29879,7 +29879,7 @@
         <v>661</v>
       </c>
       <c r="C893" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D893"/>
       <c r="E893"/>
@@ -29906,7 +29906,7 @@
         <v>662</v>
       </c>
       <c r="C894" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D894"/>
       <c r="E894"/>
@@ -29933,7 +29933,7 @@
         <v>663</v>
       </c>
       <c r="C895" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D895"/>
       <c r="E895"/>
@@ -29960,7 +29960,7 @@
         <v>750</v>
       </c>
       <c r="C896" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D896"/>
       <c r="E896"/>
@@ -29987,7 +29987,7 @@
         <v>753</v>
       </c>
       <c r="C897" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D897"/>
       <c r="E897"/>
@@ -30095,7 +30095,7 @@
         <v>758</v>
       </c>
       <c r="C901" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D901"/>
       <c r="E901"/>
@@ -30122,7 +30122,7 @@
         <v>759</v>
       </c>
       <c r="C902" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D902"/>
       <c r="E902"/>
@@ -30149,7 +30149,7 @@
         <v>760</v>
       </c>
       <c r="C903" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D903"/>
       <c r="E903"/>
@@ -30176,7 +30176,7 @@
         <v>761</v>
       </c>
       <c r="C904" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D904"/>
       <c r="E904"/>
@@ -30203,7 +30203,7 @@
         <v>762</v>
       </c>
       <c r="C905" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D905"/>
       <c r="E905"/>
@@ -30230,7 +30230,7 @@
         <v>763</v>
       </c>
       <c r="C906" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D906"/>
       <c r="E906"/>
@@ -30257,7 +30257,7 @@
         <v>764</v>
       </c>
       <c r="C907" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D907"/>
       <c r="E907"/>
@@ -30419,7 +30419,7 @@
         <v>765</v>
       </c>
       <c r="C913" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D913"/>
       <c r="E913"/>
@@ -30770,7 +30770,7 @@
         <v>778</v>
       </c>
       <c r="C926" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D926"/>
       <c r="E926"/>
@@ -41192,7 +41192,7 @@
         <v>1242</v>
       </c>
       <c r="C1312" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D1312"/>
       <c r="E1312"/>
@@ -41219,7 +41219,7 @@
         <v>1243</v>
       </c>
       <c r="C1313" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D1313"/>
       <c r="E1313"/>
@@ -41975,7 +41975,7 @@
         <v>1271</v>
       </c>
       <c r="C1341" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D1341"/>
       <c r="E1341"/>
@@ -42002,7 +42002,7 @@
         <v>1272</v>
       </c>
       <c r="C1342" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D1342"/>
       <c r="E1342"/>
@@ -42353,7 +42353,7 @@
         <v>1285</v>
       </c>
       <c r="C1355" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D1355"/>
       <c r="E1355"/>
@@ -42380,7 +42380,7 @@
         <v>1286</v>
       </c>
       <c r="C1356" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D1356"/>
       <c r="E1356"/>
@@ -43541,7 +43541,7 @@
         <v>1328</v>
       </c>
       <c r="C1399" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D1399"/>
       <c r="E1399"/>
@@ -43568,7 +43568,7 @@
         <v>1329</v>
       </c>
       <c r="C1400" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D1400"/>
       <c r="E1400"/>
@@ -43595,7 +43595,7 @@
         <v>1330</v>
       </c>
       <c r="C1401" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D1401"/>
       <c r="E1401"/>
@@ -43622,7 +43622,7 @@
         <v>1331</v>
       </c>
       <c r="C1402" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D1402"/>
       <c r="E1402"/>
@@ -43649,7 +43649,7 @@
         <v>1332</v>
       </c>
       <c r="C1403" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D1403"/>
       <c r="E1403"/>
@@ -43811,7 +43811,7 @@
         <v>1333</v>
       </c>
       <c r="C1409" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D1409"/>
       <c r="E1409"/>
@@ -45512,7 +45512,7 @@
         <v>1368</v>
       </c>
       <c r="C1472" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D1472"/>
       <c r="E1472"/>
@@ -45647,7 +45647,7 @@
         <v>1373</v>
       </c>
       <c r="C1477" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D1477"/>
       <c r="E1477"/>
@@ -45782,7 +45782,7 @@
         <v>1378</v>
       </c>
       <c r="C1482" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D1482"/>
       <c r="E1482"/>
@@ -46484,7 +46484,7 @@
         <v>1404</v>
       </c>
       <c r="C1508" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D1508"/>
       <c r="E1508"/>
@@ -46592,7 +46592,7 @@
         <v>1408</v>
       </c>
       <c r="C1512" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D1512"/>
       <c r="E1512"/>
@@ -47078,7 +47078,7 @@
         <v>1426</v>
       </c>
       <c r="C1530" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D1530"/>
       <c r="E1530"/>
@@ -47105,7 +47105,7 @@
         <v>1427</v>
       </c>
       <c r="C1531" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D1531"/>
       <c r="E1531"/>
@@ -47186,7 +47186,7 @@
         <v>1430</v>
       </c>
       <c r="C1534" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D1534"/>
       <c r="E1534"/>
@@ -47213,7 +47213,7 @@
         <v>1431</v>
       </c>
       <c r="C1535" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D1535"/>
       <c r="E1535"/>
@@ -47240,7 +47240,7 @@
         <v>1432</v>
       </c>
       <c r="C1536" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D1536"/>
       <c r="E1536"/>
@@ -47321,7 +47321,7 @@
         <v>1435</v>
       </c>
       <c r="C1539" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D1539"/>
       <c r="E1539"/>
@@ -47348,7 +47348,7 @@
         <v>1436</v>
       </c>
       <c r="C1540" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D1540"/>
       <c r="E1540"/>
@@ -47375,7 +47375,7 @@
         <v>1437</v>
       </c>
       <c r="C1541" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D1541"/>
       <c r="E1541"/>
@@ -47456,7 +47456,7 @@
         <v>1440</v>
       </c>
       <c r="C1544" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D1544"/>
       <c r="E1544"/>
@@ -47483,7 +47483,7 @@
         <v>1441</v>
       </c>
       <c r="C1545" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D1545"/>
       <c r="E1545"/>
@@ -47510,7 +47510,7 @@
         <v>1442</v>
       </c>
       <c r="C1546" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D1546"/>
       <c r="E1546"/>
@@ -47591,7 +47591,7 @@
         <v>1445</v>
       </c>
       <c r="C1549" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D1549"/>
       <c r="E1549"/>
@@ -47618,7 +47618,7 @@
         <v>1446</v>
       </c>
       <c r="C1550" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D1550"/>
       <c r="E1550"/>
@@ -47645,7 +47645,7 @@
         <v>1447</v>
       </c>
       <c r="C1551" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D1551"/>
       <c r="E1551"/>
@@ -57743,7 +57743,7 @@
         <v>1775</v>
       </c>
       <c r="C1925" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="D1925"/>
       <c r="E1925"/>
